--- a/reports/jobs_2026-08-27.xlsx
+++ b/reports/jobs_2026-08-27.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Errors" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Jobs'!$A$1:$I$89</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -525,12 +525,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>ML Embedded Software Engineer</t>
+          <t>Experienced System Test Engineer (AI/ML)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -546,7 +546,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/cambridge/ml-embedded-software-engineer/33099/97503493040</t>
+          <t>https://careers.arm.com/job/cambridge/experienced-system-test-engineer-ai-ml/33099/99807986000</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -568,12 +568,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Machine Learning Framework/Runtime Software Engineer</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -581,11 +581,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
+      <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -593,7 +589,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>https://careers.arm.com/job/noida/engineer/33099/99657761504</t>
+          <t>https://careers.arm.com/job/cambridge/machine-learning-framework-runtime-software-engineer/33099/99807985792</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -610,153 +606,145 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Arm India</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Design Engineer- Memory Design</t>
+          <t>SharePoint Full Stack role</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>Full Stack</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/SharePoint-Full-Stack-role_SR-42495-1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>https://fractal.ai/careers/</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Agnikul Cosmos</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Careers Inquiries humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>https://careers.arm.com/job/noida/design-engineer-memory-design/33099/99750827104</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>https://careers.arm.com/</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Paytm</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Product Management Intern- Paytm Gold</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Intern</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Noida, Uttar Pradesh</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/paytm/c98325df-98c4-4966-8630-4ceaa7e55909</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/paytm</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>mailto:%20humancapital@agnikul.in</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>https://agnikul.in/careers</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Zscaler India</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Software Development Engineer</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Agoda India</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Chiang Mai 1 available jobs</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1 - 3 years</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Bangalore, IND</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/zscaler/jobs/5219488007</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/zscaler</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/location/chiang-mai/</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>https://careersatagoda.com/</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Agnikul Cosmos</t>
+          <t>Agoda India</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Careers Inquiries humancapital@agnikul.in</t>
+          <t>Dubai 0 available jobs</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -769,7 +757,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Mumbai 0 available jobs Ok</t>
+        </is>
+      </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -777,12 +769,12 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>mailto:%20humancapital@agnikul.in</t>
+          <t>https://careersatagoda.com/location/dubai/</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>https://agnikul.in/careers</t>
+          <t>https://careersatagoda.com/</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -799,7 +791,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chiang Mai 1 available jobs</t>
+          <t>Mumbai 0 available jobs</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -824,7 +816,7 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/chiang-mai/</t>
+          <t>https://careersatagoda.com/location/mumbai/</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
@@ -846,7 +838,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Dubai 0 available jobs</t>
+          <t>Shanghai 1 available jobs</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -871,7 +863,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/dubai/</t>
+          <t>https://careersatagoda.com/location/shanghai/</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -893,7 +885,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs</t>
+          <t>Engineering &amp; Technology</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -906,11 +898,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai 0 available jobs Ok</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr"/>
       <c r="F10" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -918,7 +906,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai/</t>
+          <t>https://careersatagoda.com/department/technology/</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
@@ -940,7 +928,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Shanghai 1 available jobs</t>
+          <t>Mumbai jobs</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -955,7 +943,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Mumbai 0 available jobs Ok</t>
+          <t>Mumbai jobs Yokohama jobs</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -965,7 +953,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/shanghai/</t>
+          <t>https://careersatagoda.com/location/mumbai-india/</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
@@ -987,12 +975,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Engineering &amp; Technology</t>
+          <t>Backend Developer Jobs</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -1008,7 +996,7 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/department/technology/</t>
+          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
@@ -1030,12 +1018,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Mumbai jobs</t>
+          <t>Full Stack Developer Jobs</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -1043,11 +1031,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>Mumbai jobs Yokohama jobs</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -1055,7 +1039,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/location/mumbai-india/</t>
+          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
@@ -1077,12 +1061,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Backend Developer Jobs</t>
+          <t>Software Engineer Jobs</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1098,7 +1082,7 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=back%20end</t>
+          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
@@ -1115,17 +1099,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Atlan</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Developer Jobs</t>
+          <t>Field Security Engineer</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1133,7 +1117,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -1141,12 +1129,12 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=Full%20Stack</t>
+          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://jobs.ashbyhq.com/atlan</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
@@ -1158,12 +1146,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Agoda India</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer Jobs</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1184,12 +1172,12 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/vacancies/?search=software%20engineer</t>
+          <t>https://www.atlassian.com/company/careers/engineering</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>https://careersatagoda.com/</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -1201,17 +1189,17 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Atlan</t>
+          <t>Atlassian India</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Field Security Engineer</t>
+          <t>AI and Machine Learning</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1219,11 +1207,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>India</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr"/>
       <c r="F17" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -1231,12 +1215,12 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan/b2b880ed-63cd-4f56-8313-87f143fa9807</t>
+          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/atlan</t>
+          <t>https://www.atlassian.com/company/careers/all-jobs</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
@@ -1248,12 +1232,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Cloudflare India</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Customer Engineer, India (Based in Mumbai)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1266,7 +1250,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr"/>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Remote India</t>
+        </is>
+      </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -1274,12 +1262,12 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering</t>
+          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://boards.greenhouse.io/cloudflare</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
@@ -1291,17 +1279,17 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Atlassian India</t>
+          <t>Continental India</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AI and Machine Learning</t>
+          <t>Technical Service Engineer – RE</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1309,7 +1297,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>Faridabad, in</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -1317,12 +1309,12 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/engineering/ai</t>
+          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000145441139</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>https://www.atlassian.com/company/careers/all-jobs</t>
+          <t>https://careers.smartrecruiters.com/continental</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
@@ -1334,17 +1326,17 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Cloudflare India</t>
+          <t>Databricks India</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Customer Engineer, India (Based in Mumbai)</t>
+          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1354,7 +1346,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Remote India</t>
+          <t>Remote - India</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1364,12 +1356,12 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare/jobs/7955378?gh_jid=7955378</t>
+          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/cloudflare</t>
+          <t>https://boards.greenhouse.io/databricks</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
@@ -1381,12 +1373,12 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Continental India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Technical Service Engineer – RE</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1401,7 +1393,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Faridabad, in</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1411,12 +1403,12 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/continental/postings/744000145441139</t>
+          <t>https://exotel.com/about-us/careers/#op-575251-implementation-engineer</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/continental</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
@@ -1428,17 +1420,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Databricks India</t>
+          <t>Exotel</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>AI Engineer - FDE (Forward Deployed Engineer)</t>
+          <t>Implementation Engineer</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1448,7 +1440,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Remote - India</t>
+          <t>Gurgaon Full-time</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -1458,12 +1450,12 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8099751002</t>
+          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/databricks</t>
+          <t>https://exotel.com/careers/</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
@@ -1480,12 +1472,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1495,7 +1487,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1505,7 +1497,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-575251-implementation-engineer</t>
+          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
@@ -1527,12 +1519,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Implementation Engineer</t>
+          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Frontend</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1540,11 +1532,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>Gurgaon Full-time</t>
-        </is>
-      </c>
+      <c r="E24" s="4" t="inlineStr"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -1552,7 +1540,7 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-689879-implementation-engineer-</t>
+          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
@@ -1574,12 +1562,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer (PHP + React.JS)</t>
+          <t>Tech Support Intern</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1589,7 +1577,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1599,7 +1587,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-703033-integration--customisation-engineer-php--reactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-698555-tech-support-intern</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
@@ -1621,12 +1609,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Integration and Customisation Engineer - 2 (PHP+React.JS)</t>
+          <t>Product Support Intern (API Integration)</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Frontend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1634,7 +1622,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -1642,7 +1634,7 @@
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-650435-integration-and-customisation-engineer-2-phpreactjs</t>
+          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
@@ -1664,12 +1656,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Tech Support Intern</t>
+          <t>Software Engineer - 3 (Voice)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1689,7 +1681,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-698555-tech-support-intern</t>
+          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
@@ -1711,12 +1703,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Product Support Intern (API Integration)</t>
+          <t>Software Engineer 3 (Full Stack)</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1736,7 +1728,7 @@
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-685404-product-support-intern-api-integration</t>
+          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
@@ -1758,7 +1750,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Voice)</t>
+          <t>Product Head, Voice AI</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1783,7 +1775,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704555-software-engineer-3-voice</t>
+          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
@@ -1805,12 +1797,12 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 (Full Stack)</t>
+          <t>Integration &amp; Customization Engineer -1</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1820,7 +1812,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>India Full-time</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1830,7 +1822,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-697293-software-engineer-3-full-stack</t>
+          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
@@ -1852,7 +1844,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Product Head, Voice AI</t>
+          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1867,7 +1859,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bengaluru Full-time</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1877,7 +1869,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-705157-product-head-voice-ai</t>
+          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -1899,12 +1891,12 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customization Engineer -1</t>
+          <t>Software Developer - 3 (Golang/Java/Python)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -1914,7 +1906,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>India Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1924,7 +1916,7 @@
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-667737-integration--customization-engineer-1</t>
+          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
@@ -1946,7 +1938,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Integration &amp; Customisation Engineer-1 (Chatbot)</t>
+          <t>Software Engineer - 2 (Voicebot)</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1961,7 +1953,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru Full-time</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1971,7 +1963,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-638792-integration--customisation-engineer1-chatbot</t>
+          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
@@ -1993,12 +1985,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Software Developer - 3 (Golang/Java/Python)</t>
+          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -2008,7 +2000,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore Full-time</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -2018,7 +2010,7 @@
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701453-software-developer-3-golangjavapython</t>
+          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
@@ -2040,12 +2032,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 2 (Voicebot)</t>
+          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -2065,7 +2057,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-704060-software-engineer-2-voicebot</t>
+          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2082,17 +2074,17 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer - 3 (Gen AI &amp; Speech)</t>
+          <t>Ai Engg Intern</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -2102,7 +2094,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Bangalore Full-time</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2112,12 +2104,12 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-694350-software-engineer-3-gen-ai--speech</t>
+          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -2129,17 +2121,17 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Exotel</t>
+          <t>Fi Money</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer 3 -Voice &amp; Messaging (Backend)</t>
+          <t>DS/ML Intern</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -2149,7 +2141,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2159,12 +2151,12 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>https://exotel.com/about-us/careers/#op-701721-software-engineer-3-voice--messaging-backend</t>
+          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>https://exotel.com/careers/</t>
+          <t>https://jobs.lever.co/epifi</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -2181,7 +2173,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Ai Engg Intern</t>
+          <t>GenAI Product Builder Intern</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -2206,7 +2198,7 @@
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08c743e8-2b29-4f78-827e-5bd90476ed86</t>
+          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
@@ -2223,17 +2215,17 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>DS/ML Intern</t>
+          <t>UI Developer - Digital Products</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2241,11 +2233,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -2253,12 +2241,12 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/08fc1577-4593-4b94-b66b-08e638d29f37</t>
+          <t>https://fractal.ai/en-US/Careers/job/Texas/UI-Developer---Digital-Products_SR-45168-1</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -2270,17 +2258,17 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Fi Money</t>
+          <t>Fractal Analytics</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>GenAI Product Builder Intern</t>
+          <t>Snowflake_DBT Developers</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2288,11 +2276,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Bangalore</t>
-        </is>
-      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -2300,12 +2284,12 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi/4f5b7548-ea0a-4be0-816b-11d712853169</t>
+          <t>https://fractal.ai/en-US/Careers/job/New-York/Snowflake-DBT-Developers_SR-44592-1</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/epifi</t>
+          <t>https://fractal.ai/careers/</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
@@ -3230,7 +3214,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Talent Acquisition Intern</t>
+          <t>Product Management Intern- Paytm Gold</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -3255,7 +3239,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
+          <t>https://jobs.lever.co/paytm/c98325df-98c4-4966-8630-4ceaa7e55909</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3272,17 +3256,17 @@
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>PhonePe</t>
+          <t>Paytm</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>AI Video Specialist</t>
+          <t>Talent Acquisition Intern</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -3292,7 +3276,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Noida, Uttar Pradesh</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3302,12 +3286,12 @@
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7735150003</t>
+          <t>https://jobs.lever.co/paytm/08ee2a10-3268-497e-bc10-7c7fee7caa66</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/phonepe</t>
+          <t>https://jobs.lever.co/paytm</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
@@ -3324,7 +3308,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Firmware Engineer(5-7 years)</t>
+          <t>AI Video Specialist</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -3349,7 +3333,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7765845003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7735150003</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
@@ -3371,17 +3355,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Service Delivery Engineer, SRE</t>
+          <t>Firmware Engineer(5-7 years)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>DevOps / SRE</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>1-3 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -3396,7 +3380,7 @@
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7762335003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7765845003</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
@@ -3418,7 +3402,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - 2</t>
+          <t>Service Delivery Engineer, SRE</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -3428,7 +3412,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
+          <t>1-3 years</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -3443,7 +3427,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7766868003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7762335003</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -3465,17 +3449,17 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Android</t>
+          <t>Site Reliability Engineer - 2</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>DevOps / SRE</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>1-2 years</t>
+          <t>Not specified</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -3490,7 +3474,7 @@
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/phonepe/jobs/7799494003</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7766868003</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -3507,25 +3491,29 @@
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Publicis Sapient India</t>
+          <t>PhonePe</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Join our engineering talent community</t>
+          <t>Software Engineer, Android</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr"/>
+          <t>1-2 years</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -3533,12 +3521,12 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
+          <t>https://job-boards.greenhouse.io/phonepe/jobs/7799494003</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>https://careers.publicissapient.com/</t>
+          <t>https://boards.greenhouse.io/phonepe</t>
         </is>
       </c>
       <c r="I67" s="4" t="inlineStr">
@@ -3550,17 +3538,17 @@
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Quest Global</t>
+          <t>Publicis Sapient India</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Join our engineering talent community</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -3568,11 +3556,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>Indore, in</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr"/>
       <c r="F68" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -3580,12 +3564,12 @@
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
+          <t>https://careers.publicisgroupe.com/PS-Americas-MDS/talentcommunity/form?lang=en-US</t>
         </is>
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
+          <t>https://careers.publicissapient.com/</t>
         </is>
       </c>
       <c r="I68" s="4" t="inlineStr">
@@ -3602,12 +3586,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Laravel Developer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -3627,7 +3611,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738739990</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3649,12 +3633,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Node.js Developer</t>
+          <t>Laravel Developer</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -3674,7 +3658,7 @@
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738571517</t>
         </is>
       </c>
       <c r="H70" s="4" t="inlineStr">
@@ -3691,17 +3675,17 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Ramco Systems</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Internships</t>
+          <t>Node.js Developer</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -3709,7 +3693,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Indore, in</t>
+        </is>
+      </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -3717,12 +3705,12 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
+          <t>https://api.smartrecruiters.com/v1/companies/questglobaltechnologies/postings/743999738287709</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
         <is>
-          <t>https://www.ramco.com/careers/</t>
+          <t>https://careers.smartrecruiters.com/questglobaltechnologies</t>
         </is>
       </c>
       <c r="I71" s="4" t="inlineStr">
@@ -3734,17 +3722,17 @@
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Razorpay</t>
+          <t>Ramco Systems</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Internships</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -3752,11 +3740,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru</t>
-        </is>
-      </c>
+      <c r="E72" s="4" t="inlineStr"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -3764,12 +3748,12 @@
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
+          <t>https://www.ramco.com/careers/jobs-by-locations?experience=Internship</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
+          <t>https://www.ramco.com/careers/</t>
         </is>
       </c>
       <c r="I72" s="4" t="inlineStr">
@@ -3786,12 +3770,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Full Stack Builder</t>
+          <t>Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -3811,7 +3795,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4723067005</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
@@ -3828,17 +3812,17 @@
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Rubrik India</t>
+          <t>Razorpay</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Payroll Industrial Trainee</t>
+          <t>Full Stack Builder</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3848,7 +3832,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Bangalore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -3858,12 +3842,12 @@
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
+          <t>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/rubrik</t>
+          <t>https://boards.greenhouse.io/razorpaysoftwareprivatelimited</t>
         </is>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -3875,17 +3859,17 @@
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>Sarvam AI</t>
+          <t>Rubrik India</t>
         </is>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Vision</t>
+          <t>Payroll Industrial Trainee</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>AI / ML</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3895,7 +3879,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Bangalore</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -3905,12 +3889,12 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam/282019f4-f86b-4fe0-a643-bbac0cd8a751</t>
+          <t>https://www.rubrik.com/company/careers/departments/job.8070886?gh_jid=8070886</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/sarvam</t>
+          <t>https://boards.greenhouse.io/rubrik</t>
         </is>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -3922,17 +3906,17 @@
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Scaler</t>
+          <t>Sarvam AI</t>
         </is>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
+          <t>Machine Learning Engineer, Vision</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>AI / ML</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3942,7 +3926,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Remote Instructor- Python</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3952,12 +3936,12 @@
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/remote-instructor-python</t>
+          <t>https://jobs.ashbyhq.com/sarvam/282019f4-f86b-4fe0-a643-bbac0cd8a751</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>https://www.scaler.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/sarvam</t>
         </is>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -3969,17 +3953,17 @@
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
         <is>
-          <t>ShareChat</t>
+          <t>Scaler</t>
         </is>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
+          <t>Posted about 2 years ago Remote Instructor- Python Instructors - Bengaluru - Free lancer</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Backend</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3987,7 +3971,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Remote Instructor- Python</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -3995,12 +3983,12 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://www.scaler.com/careers/remote-instructor-python</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>https://sharechat.com/careers</t>
+          <t>https://www.scaler.com/careers/</t>
         </is>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -4017,12 +4005,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>AI Animator</t>
+          <t>Intern - Content Moderation (Hindi &amp; Punjabi)</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -4038,7 +4026,7 @@
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MjksInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H78" s="4" t="inlineStr">
@@ -4081,7 +4069,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTYsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4103,7 +4091,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Video Editor- AI</t>
+          <t>AI Animator</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -4124,7 +4112,7 @@
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjI0MTEsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -4141,17 +4129,17 @@
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>Shipsy</t>
+          <t>ShareChat</t>
         </is>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>QA Engineer</t>
+          <t>Video Editor- AI</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>QA / SDET</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -4159,11 +4147,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>Gurugram, in</t>
-        </is>
-      </c>
+      <c r="E81" s="4" t="inlineStr"/>
       <c r="F81" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -4171,12 +4155,12 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
+          <t>https://sharechat.mynexthire.com/employer/jobs?src=careers&amp;p=eyJwYWdlVHlwZSI6ImpkIiwiY3ZTb3VyY2UiOiJjYXJlZXJzIiwicmVxSWQiOjIzOTAsInJlcXVlc3RlciI6eyJpZCI6IiIsImNvZGUiOiIiLCJuYW1lIjoiIn0sInBhZ2UiOiJjYXJlZXJzIiwiYnVmaWx0ZXIiOi0xLCJjdXN0b21GaWVsZHMiOnt9fQ==</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/shipsy</t>
+          <t>https://sharechat.com/careers</t>
         </is>
       </c>
       <c r="I81" s="4" t="inlineStr">
@@ -4193,12 +4177,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
+          <t>QA Engineer</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Full Stack</t>
+          <t>QA / SDET</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -4218,7 +4202,7 @@
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000008330615</t>
         </is>
       </c>
       <c r="H82" s="4" t="inlineStr">
@@ -4235,17 +4219,17 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Snowflake India</t>
+          <t>Shipsy</t>
         </is>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Account Engineer</t>
+          <t>Software Engineer (Fullstack/NodeJs/ReactJs)</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Full Stack</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -4255,7 +4239,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>CO-Colombia-Remote</t>
+          <t>Gurugram, in</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -4265,12 +4249,12 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
+          <t>https://api.smartrecruiters.com/v1/companies/shipsy/postings/744000002694405</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>https://jobs.ashbyhq.com/snowflake</t>
+          <t>https://careers.smartrecruiters.com/shipsy</t>
         </is>
       </c>
       <c r="I83" s="4" t="inlineStr">
@@ -4282,17 +4266,17 @@
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
         <is>
-          <t>Sprinklr</t>
+          <t>Snowflake India</t>
         </is>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Internship and Early Careers</t>
+          <t>Account Engineer</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Intern</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -4300,7 +4284,11 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr"/>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>CO-Colombia-Remote</t>
+        </is>
+      </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -4308,12 +4296,12 @@
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
+          <t>https://jobs.ashbyhq.com/snowflake/4fafd350-a140-426f-8602-310b8d75b5fd</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>https://www.sprinklr.com/careers/</t>
+          <t>https://jobs.ashbyhq.com/snowflake</t>
         </is>
       </c>
       <c r="I84" s="4" t="inlineStr">
@@ -4325,17 +4313,17 @@
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
         <is>
-          <t>Unacademy</t>
+          <t>Sprinklr</t>
         </is>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Test Jerin</t>
+          <t>Internship and Early Careers</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Software (General)</t>
+          <t>Intern</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -4343,11 +4331,7 @@
           <t>Not specified</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>Bengaluru, in</t>
-        </is>
-      </c>
+      <c r="E85" s="4" t="inlineStr"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -4355,12 +4339,12 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
+          <t>https://www.sprinklr.com/careers/internship-and-early-careers/</t>
         </is>
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>https://careers.smartrecruiters.com/unacademy</t>
+          <t>https://www.sprinklr.com/careers/</t>
         </is>
       </c>
       <c r="I85" s="4" t="inlineStr">
@@ -4377,12 +4361,12 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Test Jerin</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Backend</t>
+          <t>Software (General)</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -4402,7 +4386,7 @@
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999710953763</t>
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr">
@@ -4419,48 +4403,142 @@
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
         <is>
+          <t>Unacademy</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Bengaluru, in</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>https://api.smartrecruiters.com/v1/companies/unacademy/postings/743999672726735</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>https://careers.smartrecruiters.com/unacademy</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>Zscaler India</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Software (General)</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>1 - 3 years</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Bangalore, IND</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="inlineStr">
+        <is>
+          <t>https://job-boards.greenhouse.io/zscaler/jobs/5219488007</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>https://boards.greenhouse.io/zscaler</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
           <t>upGrad</t>
         </is>
       </c>
-      <c r="B87" s="4" t="inlineStr">
+      <c r="B89" s="4" t="inlineStr">
         <is>
           <t>Data Science Bootcamp with AI</t>
         </is>
       </c>
-      <c r="C87" s="4" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>Software (General)</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
-        <is>
-          <t>Not specified</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr"/>
-      <c r="F87" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>Not specified</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr"/>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
         <is>
           <t>https://www.upgrad.com/bootcamps/job-linked-data-science-advanced-bootcamp/</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr">
+      <c r="H89" s="4" t="inlineStr">
         <is>
           <t>https://www.upgrad.com/careers/</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr">
+      <c r="I89" s="4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I87"/>
+  <autoFilter ref="A1:I89"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId2"/>
@@ -4548,6 +4626,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4559,7 +4639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4647,55 +4727,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ather Energy</t>
+          <t>Nykaa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.atherenergy.com/careers</t>
+          <t>https://www.nykaa.com/careers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.atherenergy.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Darwinbox</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://darwinbox.com/careers</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://darwinbox.com/careers", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Nykaa</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.nykaa.com/careers</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.nykaa.com/careers
 Call log:
@@ -4704,18 +4744,18 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Juspay</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>https://juspay.io/careers</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4724,18 +4764,18 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>MakeMyTrip</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>https://careers.makemytrip.com/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4744,18 +4784,38 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FirstCry</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.firstcry.com/careers</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
+Call log:
+  - navigating to "https://www.firstcry.com/careers", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>PharmEasy</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://pharmeasy.in/careers</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
@@ -4764,18 +4824,18 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Zomato</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>https://www.zomato.com/careers</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.zomato.com/careers
 Call log:
@@ -4784,38 +4844,18 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Shiprocket</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>https://www.shiprocket.in/careers/</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
-Call log:
-  - navigating to "https://www.shiprocket.in/careers/", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Coforge</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.coforge.com/careers</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.coforge.com/careers
 Call log:
@@ -4824,18 +4864,18 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Persistent Systems</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>https://www.persistent.com/careers/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: net::ERR_HTTP2_PROTOCOL_ERROR at https://www.persistent.com/careers/
 Call log:
@@ -4844,18 +4884,18 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Udaan</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>https://udaan.com/careers</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t xml:space="preserve">playwright failed: Page.goto: Timeout 25000ms exceeded.
 Call log:
